--- a/Excel/OccupationTwoConfig.xlsx
+++ b/Excel/OccupationTwoConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8BC11E-1F56-4F34-90A8-69AA8AD73A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC1CFB1B-93EA-4592-AF1E-DF78728E3682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -59,7 +59,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="O3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="127">
   <si>
     <t>Id</t>
   </si>
@@ -463,6 +463,80 @@
   <si>
     <t>法杖精通：使用法杖类武器伤害提升5%,装备精通：轻甲,双防光环：附近己方单位防御效果增加10%</t>
     <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>OccupationName_EN</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>OccDes_EN</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wind Runner</t>
+  </si>
+  <si>
+    <t>Swordmaster</t>
+  </si>
+  <si>
+    <t>Magi Warrior</t>
+  </si>
+  <si>
+    <t>Magical Sorcerer</t>
+  </si>
+  <si>
+    <t>Light Spirit Messenger</t>
+  </si>
+  <si>
+    <t>Divine Priest</t>
+  </si>
+  <si>
+    <t>Survival Master</t>
+  </si>
+  <si>
+    <t>Warlock</t>
+  </si>
+  <si>
+    <t>Zookeeper</t>
+  </si>
+  <si>
+    <t>Shadow Magic</t>
+  </si>
+  <si>
+    <t>The Wind Messenger</t>
+  </si>
+  <si>
+    <t>Shadow Priest Speed reduction</t>
+  </si>
+  <si>
+    <t>Speed specialization: Movement speed increases by 10%, Equipment proficiency: Light armor, Movement aura: Movement speed within the team increases by 10%</t>
+  </si>
+  <si>
+    <t>Sword Specialization: Increases damage from sword-based weapons by 5%. Equipment Proficiency: Light Armor. Critical Strike Aura: Increases critical strike chance within the squad by 5%.</t>
+  </si>
+  <si>
+    <t>Specialization in weapons: Using melee weapons increases damage by 5%. Equipment proficiency: Heavy armor, Damage aura: The damage caused within the team is increased by 5%.</t>
+  </si>
+  <si>
+    <t>Scepter Mastery: Damage from using scepter-type weapons increases by 5%. Equipment Mastery: Leather Armor, Double Defense Aura: The defensive effect of nearby friendly units increases by 10%.</t>
+  </si>
+  <si>
+    <t>Magic Book Specialization: Damage from magic book-type weapons increases by 5%. Equipment Proficiency: Leather Armor, Slow Aura: The movement speed of nearby enemy units is reduced by 10%.</t>
+  </si>
+  <si>
+    <t>Skill Mastery: Skill effect increases by 10%, Equipment Mastery: Heavy Armor, Aura of the Mind: Enemy units within range receive an additional 10% damage</t>
+  </si>
+  <si>
+    <t>Archery Expertise: Increases the damage of bow and arrow weapons by 5%. Equipment Proficiency: Armor, Physical Penetration Aura: Increases physical penetration within the squad by 10%.</t>
+  </si>
+  <si>
+    <t>Archery Proficiency: Damage from archery weapons increases by 5%, Equipment Proficiency: Light Armor, Heavy Strike Aura: The probability of heavy strikes within the team increases by 5%</t>
+  </si>
+  <si>
+    <t>Bow Expertise: Damage from bow weapons increases by 5%. Equipment Mastery: Heavy armor, Beast Aura: The attributes of summoned creatures and pets within the squad are enhanced by 10%</t>
+  </si>
+  <si>
+    <t>Staff Mastery: Damage from using staff-based weapons increases by 5%. Equipment Mastery: Light Armor, Double Defense Aura: The defense effect of nearby friendly units increases by 10%</t>
   </si>
 </sst>
 </file>
@@ -2373,25 +2447,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:M40"/>
+  <dimension ref="C1:O40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="9.375" customWidth="1"/>
     <col min="4" max="4" width="15.125" customWidth="1"/>
-    <col min="5" max="5" width="71.375" customWidth="1"/>
-    <col min="6" max="6" width="68" customWidth="1"/>
-    <col min="7" max="7" width="38.375" customWidth="1"/>
-    <col min="8" max="8" width="56.25" customWidth="1"/>
-    <col min="9" max="9" width="22.375" customWidth="1"/>
-    <col min="10" max="10" width="18.875" customWidth="1"/>
-    <col min="11" max="11" width="23.75" customWidth="1"/>
-    <col min="12" max="12" width="46.25" customWidth="1"/>
-    <col min="13" max="13" width="68.375" customWidth="1"/>
+    <col min="5" max="5" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="71.375" customWidth="1"/>
+    <col min="8" max="8" width="68" customWidth="1"/>
+    <col min="9" max="9" width="38.375" customWidth="1"/>
+    <col min="10" max="10" width="56.25" customWidth="1"/>
+    <col min="11" max="11" width="22.375" customWidth="1"/>
+    <col min="12" max="12" width="18.875" customWidth="1"/>
+    <col min="13" max="13" width="23.75" customWidth="1"/>
+    <col min="14" max="14" width="46.25" customWidth="1"/>
+    <col min="15" max="15" width="68.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="3:15" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2399,34 +2474,40 @@
         <v>1</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -2434,34 +2515,40 @@
         <v>11</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="M4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="N4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="3" t="s">
         <v>20</v>
       </c>
@@ -2472,31 +2559,37 @@
         <v>21</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="N5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="O5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="8">
         <v>101</v>
       </c>
@@ -2504,34 +2597,40 @@
         <v>23</v>
       </c>
       <c r="E6" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="G6" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H6" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="I6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="J6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="K6" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J6" s="10">
+      <c r="L6" s="10">
         <v>1</v>
       </c>
-      <c r="K6" s="10">
+      <c r="M6" s="10">
         <v>12</v>
       </c>
-      <c r="L6" s="13" t="s">
+      <c r="N6" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="14" t="s">
+      <c r="O6" s="14" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="8">
         <v>102</v>
       </c>
@@ -2539,34 +2638,40 @@
         <v>30</v>
       </c>
       <c r="E7" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="G7" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="I7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="J7" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="K7" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="10">
+      <c r="L7" s="10">
         <v>1</v>
       </c>
-      <c r="K7" s="10">
+      <c r="M7" s="10">
         <v>12</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="N7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="M7" s="14" t="s">
+      <c r="O7" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="8">
         <v>103</v>
       </c>
@@ -2574,34 +2679,40 @@
         <v>36</v>
       </c>
       <c r="E8" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="G8" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="I8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="J8" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="K8" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="10">
+      <c r="L8" s="10">
         <v>2</v>
       </c>
-      <c r="K8" s="10">
+      <c r="M8" s="10">
         <v>13</v>
       </c>
-      <c r="L8" s="13" t="s">
+      <c r="N8" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="M8" s="14" t="s">
+      <c r="O8" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="8">
         <v>201</v>
       </c>
@@ -2609,34 +2720,40 @@
         <v>42</v>
       </c>
       <c r="E9" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="G9" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="H9" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="I9" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="J9" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="K9" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J9" s="10">
+      <c r="L9" s="10">
         <v>3</v>
       </c>
-      <c r="K9" s="10">
+      <c r="M9" s="10">
         <v>11</v>
       </c>
-      <c r="L9" s="13" t="s">
+      <c r="N9" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="M9" s="14" t="s">
+      <c r="O9" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="8">
         <v>202</v>
       </c>
@@ -2644,34 +2761,40 @@
         <v>49</v>
       </c>
       <c r="E10" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="G10" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="I10" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="J10" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="K10" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="10">
+      <c r="L10" s="10">
         <v>4</v>
       </c>
-      <c r="K10" s="10">
+      <c r="M10" s="10">
         <v>11</v>
       </c>
-      <c r="L10" s="13" t="s">
+      <c r="N10" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="M10" s="14" t="s">
+      <c r="O10" s="14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="8">
         <v>203</v>
       </c>
@@ -2679,34 +2802,40 @@
         <v>55</v>
       </c>
       <c r="E11" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="G11" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H11" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="I11" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="J11" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="K11" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="J11" s="10">
+      <c r="L11" s="10">
         <v>4</v>
       </c>
-      <c r="K11" s="10">
+      <c r="M11" s="10">
         <v>13</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="N11" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="M11" s="14" t="s">
+      <c r="O11" s="14" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="8">
         <v>301</v>
       </c>
@@ -2714,34 +2843,40 @@
         <v>61</v>
       </c>
       <c r="E12" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="G12" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H12" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="I12" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="J12" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="K12" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="J12" s="10">
+      <c r="L12" s="10">
         <v>5</v>
       </c>
-      <c r="K12" s="10">
+      <c r="M12" s="10">
         <v>11</v>
       </c>
-      <c r="L12" s="13" t="s">
+      <c r="N12" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="M12" s="14" t="s">
+      <c r="O12" s="14" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C13" s="8">
         <v>302</v>
       </c>
@@ -2749,34 +2884,40 @@
         <v>64</v>
       </c>
       <c r="E13" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="G13" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="I13" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="J13" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="K13" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J13" s="10">
+      <c r="L13" s="10">
         <v>5</v>
       </c>
-      <c r="K13" s="10">
+      <c r="M13" s="10">
         <v>12</v>
       </c>
-      <c r="L13" s="13" t="s">
+      <c r="N13" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M13" s="14" t="s">
+      <c r="O13" s="14" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C14" s="8">
         <v>303</v>
       </c>
@@ -2784,34 +2925,40 @@
         <v>68</v>
       </c>
       <c r="E14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="G14" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="H14" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="I14" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="J14" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="K14" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="J14" s="10">
+      <c r="L14" s="10">
         <v>5</v>
       </c>
-      <c r="K14" s="10">
+      <c r="M14" s="10">
         <v>13</v>
       </c>
-      <c r="L14" s="13" t="s">
+      <c r="N14" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="M14" s="14" t="s">
+      <c r="O14" s="14" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="8">
         <v>401</v>
       </c>
@@ -2819,34 +2966,40 @@
         <v>94</v>
       </c>
       <c r="E15" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="G15" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="H15" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="I15" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="J15" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="I15" s="13" t="s">
+      <c r="K15" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J15" s="10">
+      <c r="L15" s="10">
         <v>3</v>
       </c>
-      <c r="K15" s="10">
+      <c r="M15" s="10">
         <v>12</v>
       </c>
-      <c r="L15" s="13" t="s">
+      <c r="N15" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="14" t="s">
+      <c r="O15" s="14" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C16" s="8">
         <v>402</v>
       </c>
@@ -2854,34 +3007,40 @@
         <v>90</v>
       </c>
       <c r="E16" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F16" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="G16" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H16" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="I16" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="J16" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="I16" s="13" t="s">
+      <c r="K16" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="J16" s="10">
+      <c r="L16" s="10">
         <v>4</v>
       </c>
-      <c r="K16" s="10">
+      <c r="M16" s="10">
         <v>11</v>
       </c>
-      <c r="L16" s="13" t="s">
+      <c r="N16" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="M16" s="14" t="s">
+      <c r="O16" s="14" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="8">
         <v>403</v>
       </c>
@@ -2889,48 +3048,54 @@
         <v>95</v>
       </c>
       <c r="E17" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="G17" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H17" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="I17" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="J17" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="I17" s="13" t="s">
+      <c r="K17" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="J17" s="10">
+      <c r="L17" s="10">
         <v>3</v>
       </c>
-      <c r="K17" s="10">
+      <c r="M17" s="10">
         <v>13</v>
       </c>
-      <c r="L17" s="13" t="s">
+      <c r="N17" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="M17" s="14" t="s">
+      <c r="O17" s="14" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/Excel/OccupationTwoConfig.xlsx
+++ b/Excel/OccupationTwoConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC1CFB1B-93EA-4592-AF1E-DF78728E3682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBC3CAB-F8B8-4BA9-8EAC-0591B604FD41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OccupationTwoConfig" sheetId="1" r:id="rId1"/>
@@ -2452,7 +2452,7 @@
   <cols>
     <col min="3" max="3" width="9.375" customWidth="1"/>
     <col min="4" max="4" width="15.125" customWidth="1"/>
-    <col min="5" max="5" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.75" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="71.375" customWidth="1"/>
     <col min="8" max="8" width="68" customWidth="1"/>
     <col min="9" max="9" width="38.375" customWidth="1"/>

--- a/Excel/OccupationTwoConfig.xlsx
+++ b/Excel/OccupationTwoConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBC3CAB-F8B8-4BA9-8EAC-0591B604FD41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8FB3E7-B151-464F-B94C-6CE784AD1EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OccupationTwoConfig" sheetId="1" r:id="rId1"/>
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="130">
   <si>
     <t>Id</t>
   </si>
@@ -537,6 +537,15 @@
   </si>
   <si>
     <t>Staff Mastery: Damage from using staff-based weapons increases by 5%. Equipment Mastery: Light Armor, Double Defense Aura: The defense effect of nearby friendly units increases by 10%</t>
+  </si>
+  <si>
+    <t>巨剑守护</t>
+  </si>
+  <si>
+    <t>破风者</t>
+  </si>
+  <si>
+    <t>巨神战士</t>
   </si>
 </sst>
 </file>
@@ -3081,9 +3090,129 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C18" s="8">
+        <v>501</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18" s="10">
+        <v>1</v>
+      </c>
+      <c r="M18" s="10">
+        <v>12</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="O18" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C19" s="8">
+        <v>502</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="L19" s="10">
+        <v>1</v>
+      </c>
+      <c r="M19" s="10">
+        <v>12</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="O19" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C20" s="8">
+        <v>503</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="L20" s="10">
+        <v>2</v>
+      </c>
+      <c r="M20" s="10">
+        <v>13</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="O20" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
     <row r="21" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/Excel/OccupationTwoConfig.xlsx
+++ b/Excel/OccupationTwoConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8FB3E7-B151-464F-B94C-6CE784AD1EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135FD77A-1374-4BB2-85EE-2087857CC3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OccupationTwoConfig" sheetId="1" r:id="rId1"/>
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="133">
   <si>
     <t>Id</t>
   </si>
@@ -539,13 +539,28 @@
     <t>Staff Mastery: Damage from using staff-based weapons increases by 5%. Equipment Mastery: Light Armor, Double Defense Aura: The defense effect of nearby friendly units increases by 10%</t>
   </si>
   <si>
+    <t>63401001,63401002,63401003,63401004,65021101,65021201,65021301,65021401</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>63402001,63402002,63402003,63402004,65022101,65022201,65022301,65022401</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>63403001,63403002,63403003,63403004,65023101,65023201,65023301,65023401</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>泰坦之灵</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
     <t>巨剑守护</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>破风者</t>
-  </si>
-  <si>
-    <t>巨神战士</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3095,19 +3110,15 @@
         <v>501</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>105</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G18" s="9" t="s">
-        <v>117</v>
-      </c>
+      <c r="G18" s="9"/>
       <c r="H18" s="11" t="s">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>25</v>
@@ -3136,19 +3147,15 @@
         <v>502</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>106</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G19" s="9" t="s">
-        <v>118</v>
-      </c>
+      <c r="G19" s="9"/>
       <c r="H19" s="11" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="I19" s="12" t="s">
         <v>25</v>
@@ -3177,19 +3184,15 @@
         <v>503</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>107</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G20" s="9" t="s">
-        <v>119</v>
-      </c>
+      <c r="G20" s="9"/>
       <c r="H20" s="11" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="I20" s="12" t="s">
         <v>25</v>

--- a/Excel/OccupationTwoConfig.xlsx
+++ b/Excel/OccupationTwoConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135FD77A-1374-4BB2-85EE-2087857CC3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{581050A0-B6CF-4151-9F65-82547364A3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="136">
   <si>
     <t>Id</t>
   </si>
@@ -560,6 +560,18 @@
   </si>
   <si>
     <t>破风者</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>63401001,63401004,65021101,65021201,65021301,65021401</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>63402001,63402004,65022101,65022201,65022301,65022401</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>63403001,63403004,65023101,65023201,65023301,65023401</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -3124,7 +3136,7 @@
         <v>25</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>26</v>
+        <v>133</v>
       </c>
       <c r="K18" s="13" t="s">
         <v>27</v>
@@ -3161,7 +3173,7 @@
         <v>25</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="K19" s="13" t="s">
         <v>33</v>
@@ -3198,7 +3210,7 @@
         <v>25</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="K20" s="13" t="s">
         <v>39</v>

--- a/Excel/OccupationTwoConfig.xlsx
+++ b/Excel/OccupationTwoConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{581050A0-B6CF-4151-9F65-82547364A3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83410A0C-3CE0-4529-93E9-5DFBF635A491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="137">
   <si>
     <t>Id</t>
   </si>
@@ -573,6 +573,9 @@
   <si>
     <t>63403001,63403004,65023101,65023201,65023301,65023401</t>
     <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>50001,50002,50003,50011,50012,50013,50021,50022,50023,50031,50032,50033,50041,50042,50043,50051,50052,50053,50061,50062,50063</t>
   </si>
 </sst>
 </file>
@@ -3133,7 +3136,7 @@
         <v>127</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>25</v>
+        <v>136</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>133</v>
@@ -3170,7 +3173,7 @@
         <v>128</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>25</v>
+        <v>136</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>134</v>
@@ -3207,7 +3210,7 @@
         <v>129</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>25</v>
+        <v>136</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>135</v>

--- a/Excel/OccupationTwoConfig.xlsx
+++ b/Excel/OccupationTwoConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83410A0C-3CE0-4529-93E9-5DFBF635A491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6593A310-26FB-4369-AD56-6A09C6E98934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="141">
   <si>
     <t>Id</t>
   </si>
@@ -576,6 +576,19 @@
   </si>
   <si>
     <t>50001,50002,50003,50011,50012,50013,50021,50022,50023,50031,50032,50033,50041,50042,50043,50051,50052,50053,50061,50062,50063</t>
+  </si>
+  <si>
+    <t>69055001,69055002,69055003,69055011,69055012,69055013,69055014,60031231</t>
+  </si>
+  <si>
+    <t>69055001,69055002,69055003,69055021,69055022,69055023,69055024,60031241</t>
+  </si>
+  <si>
+    <t>69055001,69055002,69055003,69055031,69055032,69055033,69055034,60031255</t>
+  </si>
+  <si>
+    <t>40000103,40000203</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3154,7 +3167,7 @@
         <v>28</v>
       </c>
       <c r="O18" s="14" t="s">
-        <v>29</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -3191,7 +3204,7 @@
         <v>34</v>
       </c>
       <c r="O19" s="14" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -3225,10 +3238,10 @@
         <v>13</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>41</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/Excel/OccupationTwoConfig.xlsx
+++ b/Excel/OccupationTwoConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6593A310-26FB-4369-AD56-6A09C6E98934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09958BC-5424-4327-90C2-077A2FA308B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OccupationTwoConfig" sheetId="1" r:id="rId1"/>
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="151">
   <si>
     <t>Id</t>
   </si>
@@ -485,9 +485,6 @@
     <t>Magical Sorcerer</t>
   </si>
   <si>
-    <t>Light Spirit Messenger</t>
-  </si>
-  <si>
     <t>Divine Priest</t>
   </si>
   <si>
@@ -503,12 +500,6 @@
     <t>Shadow Magic</t>
   </si>
   <si>
-    <t>The Wind Messenger</t>
-  </si>
-  <si>
-    <t>Shadow Priest Speed reduction</t>
-  </si>
-  <si>
     <t>Speed specialization: Movement speed increases by 10%, Equipment proficiency: Light armor, Movement aura: Movement speed within the team increases by 10%</t>
   </si>
   <si>
@@ -588,6 +579,57 @@
   </si>
   <si>
     <t>40000103,40000203</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Greatsword Guard</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shadow Priest</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Light Spirit</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wind Messenger</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Windbreaker</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Titan Spirit</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能精通：技能效果提升10%,装备精通：重甲,心灵光环：附近敌方单位受到伤害额外提升10%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>刀类专精：使用刀类武器伤害提升5%,装备精通：重甲,反弹光环：受到伤害10%概率反弹100%伤害</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blade Mastery: Damage with blade weapons increased by 5%；Equipment Proficiency: Heavy Armor；Reflection Aura: 10% chance to reflect 100% of received damage</t>
+  </si>
+  <si>
+    <t>刀类专精：使用刀类武器伤害提升5%,装备精通：轻甲,冷却光环：小队内所有队员技能冷却时间降低10%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻速专精：攻击速度提升20%,装备精通：重甲,攻速光环：小队内所有队员攻击速度提升10%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blade Mastery:Damage with blade weapons increased by 5%;Equipment Proficiency:Light Armor;Cooldown Aura:Skill cooldown of all party members reduced by 10%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack Speed Mastery:Attack speed increased by 20%;Equipment Proficiency:Heavy Armor;Attack Speed Aura:Attack speed of all party members increased by 10%</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2504,8 +2546,9 @@
   <cols>
     <col min="3" max="3" width="9.375" customWidth="1"/>
     <col min="4" max="4" width="15.125" customWidth="1"/>
-    <col min="5" max="5" width="28.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="71.375" customWidth="1"/>
+    <col min="5" max="5" width="35.375" customWidth="1"/>
+    <col min="6" max="6" width="77.625" customWidth="1"/>
+    <col min="7" max="7" width="71.375" customWidth="1"/>
     <col min="8" max="8" width="68" customWidth="1"/>
     <col min="9" max="9" width="38.375" customWidth="1"/>
     <col min="10" max="10" width="56.25" customWidth="1"/>
@@ -2655,7 +2698,7 @@
         <v>24</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>85</v>
@@ -2696,7 +2739,7 @@
         <v>31</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>79</v>
@@ -2737,7 +2780,7 @@
         <v>37</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>88</v>
@@ -2778,7 +2821,7 @@
         <v>43</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>84</v>
@@ -2813,13 +2856,13 @@
         <v>49</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>50</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>83</v>
@@ -2854,13 +2897,13 @@
         <v>55</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>56</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>82</v>
@@ -2895,13 +2938,13 @@
         <v>61</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>73</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>81</v>
@@ -2936,13 +2979,13 @@
         <v>64</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>74</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>87</v>
@@ -2977,13 +3020,13 @@
         <v>68</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>75</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H14" s="11" t="s">
         <v>80</v>
@@ -3018,13 +3061,13 @@
         <v>94</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>102</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>100</v>
@@ -3059,13 +3102,13 @@
         <v>90</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>50</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>101</v>
@@ -3100,13 +3143,13 @@
         <v>95</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>56</v>
+        <v>144</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H17" s="11" t="s">
         <v>99</v>
@@ -3138,21 +3181,25 @@
         <v>501</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E18" s="9"/>
+        <v>128</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>138</v>
+      </c>
       <c r="F18" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" s="9"/>
+        <v>145</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>146</v>
+      </c>
       <c r="H18" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K18" s="13" t="s">
         <v>27</v>
@@ -3167,7 +3214,7 @@
         <v>28</v>
       </c>
       <c r="O18" s="14" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -3175,21 +3222,25 @@
         <v>502</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="E19" s="9"/>
+        <v>129</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>142</v>
+      </c>
       <c r="F19" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" s="9"/>
+        <v>147</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>149</v>
+      </c>
       <c r="H19" s="11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K19" s="13" t="s">
         <v>33</v>
@@ -3204,7 +3255,7 @@
         <v>34</v>
       </c>
       <c r="O19" s="14" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -3212,21 +3263,25 @@
         <v>503</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E20" s="9"/>
+        <v>127</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>143</v>
+      </c>
       <c r="F20" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G20" s="9"/>
+        <v>148</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>150</v>
+      </c>
       <c r="H20" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K20" s="13" t="s">
         <v>39</v>
@@ -3238,10 +3293,10 @@
         <v>13</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3267,7 +3322,7 @@
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Excel/OccupationTwoConfig.xlsx
+++ b/Excel/OccupationTwoConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09958BC-5424-4327-90C2-077A2FA308B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEFC5AFE-4DF0-4BA5-B050-CA98CB38A15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OccupationTwoConfig" sheetId="1" r:id="rId1"/>
@@ -3208,7 +3208,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N18" s="13" t="s">
         <v>28</v>

--- a/Excel/OccupationTwoConfig.xlsx
+++ b/Excel/OccupationTwoConfig.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEFC5AFE-4DF0-4BA5-B050-CA98CB38A15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31B340A-A52D-4A10-BE51-FE5D7F65B58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OccupationTwoConfig" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -3205,7 +3205,7 @@
         <v>27</v>
       </c>
       <c r="L18" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18" s="10">
         <v>13</v>
@@ -3246,7 +3246,7 @@
         <v>33</v>
       </c>
       <c r="L19" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19" s="10">
         <v>12</v>

--- a/Excel/OccupationTwoConfig.xlsx
+++ b/Excel/OccupationTwoConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31B340A-A52D-4A10-BE51-FE5D7F65B58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05AC831-E1A0-48EC-8034-B64AB88B8E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -575,9 +575,6 @@
     <t>69055001,69055002,69055003,69055021,69055022,69055023,69055024,60031241</t>
   </si>
   <si>
-    <t>69055001,69055002,69055003,69055031,69055032,69055033,69055034,60031255</t>
-  </si>
-  <si>
     <t>40000103,40000203</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -630,6 +627,10 @@
   </si>
   <si>
     <t>Attack Speed Mastery:Attack speed increased by 20%;Equipment Proficiency:Heavy Armor;Attack Speed Aura:Attack speed of all party members increased by 10%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>69055001,69055002,69055003,69055031,69055032,69055033,69055034,60031251</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2856,7 +2857,7 @@
         <v>49</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>50</v>
@@ -3102,7 +3103,7 @@
         <v>90</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>50</v>
@@ -3143,10 +3144,10 @@
         <v>95</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G17" s="9" t="s">
         <v>119</v>
@@ -3184,13 +3185,13 @@
         <v>128</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F18" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="G18" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>124</v>
@@ -3225,13 +3226,13 @@
         <v>129</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H19" s="11" t="s">
         <v>125</v>
@@ -3266,13 +3267,13 @@
         <v>127</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H20" s="11" t="s">
         <v>126</v>
@@ -3293,10 +3294,10 @@
         <v>13</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
